--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.020797289396148</v>
+        <v>0.9783795595268741</v>
       </c>
       <c r="D2" t="n">
-        <v>9.049712113161245</v>
+        <v>1.470578218388702</v>
       </c>
       <c r="E2" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F2" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.433034373659253</v>
+        <v>1.207868085719629</v>
       </c>
       <c r="D3" t="n">
-        <v>17.63297673697886</v>
+        <v>2.865358719759064</v>
       </c>
       <c r="E3" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F3" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.14418971907665</v>
+        <v>3.110930829349955</v>
       </c>
       <c r="D4" t="n">
-        <v>24.10753788968768</v>
+        <v>3.917474907074248</v>
       </c>
       <c r="E4" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F4" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.17685890085664</v>
+        <v>3.603739571389205</v>
       </c>
       <c r="D5" t="n">
-        <v>15.83922394213693</v>
+        <v>2.573873890597251</v>
       </c>
       <c r="E5" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F5" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.76154610274641</v>
+        <v>2.723751241696291</v>
       </c>
       <c r="D6" t="n">
-        <v>17.15178684708086</v>
+        <v>2.787165362650641</v>
       </c>
       <c r="E6" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F6" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.371412885511</v>
+        <v>4.772854593895537</v>
       </c>
       <c r="D7" t="n">
-        <v>27.15075338905555</v>
+        <v>4.411997425721527</v>
       </c>
       <c r="E7" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F7" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53203750350731</v>
+        <v>4.473956094319938</v>
       </c>
       <c r="D8" t="n">
-        <v>8.139410298049853</v>
+        <v>1.322654173433101</v>
       </c>
       <c r="E8" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F8" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.01952475259191</v>
+        <v>4.553172772296186</v>
       </c>
       <c r="D9" t="n">
-        <v>37.03039292257105</v>
+        <v>6.017438849917795</v>
       </c>
       <c r="E9" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F9" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.03906433678505</v>
+        <v>3.418847954727571</v>
       </c>
       <c r="D10" t="n">
-        <v>5.315072906367325</v>
+        <v>0.8636993472846903</v>
       </c>
       <c r="E10" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F10" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28643905646242</v>
+        <v>3.134046346675143</v>
       </c>
       <c r="D11" t="n">
-        <v>22.61083810919003</v>
+        <v>3.674261192743379</v>
       </c>
       <c r="E11" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F11" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11.62801190395255</v>
+        <v>1.88955193439229</v>
       </c>
       <c r="D12" t="n">
-        <v>13.85823041837247</v>
+        <v>2.251962442985526</v>
       </c>
       <c r="E12" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F12" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.773738083857273</v>
+        <v>1.588232438626807</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3847010032621</v>
+        <v>2.337513913030091</v>
       </c>
       <c r="E13" t="n">
-        <v>7.717819180040414</v>
+        <v>1.254145616756567</v>
       </c>
       <c r="F13" t="n">
-        <v>8.550287527771648</v>
+        <v>1.389421723262893</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
